--- a/proposal/others/21B_Min_Genesis_Mission_Phase_Application_Template.xlsx
+++ b/proposal/others/21B_Min_Genesis_Mission_Phase_Application_Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB53CFFC-61B8-1949-B9F0-6BE11EF58A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096FFB46-EB2E-B644-96DE-F499A15868EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="660" windowWidth="33040" windowHeight="17600" xr2:uid="{22B5A4FB-6387-446F-8BA9-19021887B1CE}"/>
+    <workbookView xWindow="3860" yWindow="2760" windowWidth="33040" windowHeight="17600" activeTab="1" xr2:uid="{22B5A4FB-6387-446F-8BA9-19021887B1CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Phase I Summary" sheetId="1" r:id="rId1"/>
@@ -884,7 +884,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -940,6 +940,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -960,6 +961,15 @@
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -1657,15 +1667,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1685,57 +1686,57 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EE1A5BCD-A536-461F-A3E8-C45BE6D0D2C8}" name="PITable" displayName="PITable" ref="A6:H15" totalsRowShown="0" headerRowDxfId="37" headerRowBorderDxfId="36" tableBorderDxfId="35" totalsRowBorderDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EE1A5BCD-A536-461F-A3E8-C45BE6D0D2C8}" name="PITable" displayName="PITable" ref="A6:H15" totalsRowShown="0" headerRowDxfId="40" headerRowBorderDxfId="39" tableBorderDxfId="38" totalsRowBorderDxfId="37">
   <autoFilter ref="A6:H15" xr:uid="{EE1A5BCD-A536-461F-A3E8-C45BE6D0D2C8}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{45CC0D4E-E00C-415E-AA20-BFB5C852B809}" name="Lead PI" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{982927EA-F02B-4FBA-9C3D-0FC36B88221D}" name="Last Name" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{A6072002-61FB-42B0-B7A2-0B51D108A993}" name="First Name" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{CC5912FA-CE2C-487C-92D5-B134C22DECE6}" name="Institution" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{BE3B2A79-1360-4419-AA16-E6ED6FA5B815}" name="Email address" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{FAFC272E-BC01-4A87-8135-188DBC9AFDD1}" name="Position" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{8117A28F-983F-455C-92C6-6609FE6ADD13}" name="ORCID (optional)" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{CBAC69C4-C2E2-4C62-A8EB-936548C78CB7}" name="Expertise" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{45CC0D4E-E00C-415E-AA20-BFB5C852B809}" name="Lead PI" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{982927EA-F02B-4FBA-9C3D-0FC36B88221D}" name="Last Name" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{A6072002-61FB-42B0-B7A2-0B51D108A993}" name="First Name" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{CC5912FA-CE2C-487C-92D5-B134C22DECE6}" name="Institution" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{BE3B2A79-1360-4419-AA16-E6ED6FA5B815}" name="Email address" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{FAFC272E-BC01-4A87-8135-188DBC9AFDD1}" name="Position" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{8117A28F-983F-455C-92C6-6609FE6ADD13}" name="ORCID (optional)" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{CBAC69C4-C2E2-4C62-A8EB-936548C78CB7}" name="Expertise" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5C996A85-ACD9-4C80-9C41-7456E9C01AA0}" name="BudgetTable" displayName="BudgetTable" ref="A2:B10" totalsRowCount="1" headerRowDxfId="25" dataDxfId="23" totalsRowDxfId="21" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5C996A85-ACD9-4C80-9C41-7456E9C01AA0}" name="BudgetTable" displayName="BudgetTable" ref="A2:B10" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" totalsRowDxfId="24" headerRowBorderDxfId="27" tableBorderDxfId="25" totalsRowBorderDxfId="23">
   <autoFilter ref="A2:B9" xr:uid="{5C996A85-ACD9-4C80-9C41-7456E9C01AA0}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C9AA7590-4640-4396-A021-FB32F82AD2D3}" name="Institution" totalsRowLabel="Total" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{23A07196-D24B-4DA9-945C-44993284CEEA}" name="Budget $" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{C9AA7590-4640-4396-A021-FB32F82AD2D3}" name="Institution" totalsRowLabel="Total" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{23A07196-D24B-4DA9-945C-44993284CEEA}" name="Budget $" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BDE630A-80E6-49CC-8B0C-050010869B2B}" name="Table1" displayName="Table1" ref="A15:J23" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BDE630A-80E6-49CC-8B0C-050010869B2B}" name="Table1" displayName="Table1" ref="A15:J23" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A15:J23" xr:uid="{7B26134D-B1D6-4E79-8F17-F5206D835DF6}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{0420DE82-AF93-48EB-905E-6D6E97C7D46A}" name="Allocation Program or Source (If existing allocation will be used)" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{F1802CDB-6A94-45A1-B4B7-F47A46CBC422}" name="Machine" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{D0E49B48-EDA7-4D05-92EC-C7F04F018CEE}" name="Estimated Compute Need" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{9997A077-AD03-480D-AF28-F4401B03DEA1}" name="Compute Need Units" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{CD58E2CE-CF0D-48A0-804A-1D51CC263494}" name="Project Number " dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{57020889-5267-4603-94CB-C38C2ADD54FC}" name="Expected data storage (TB)" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{756AB4E2-DC44-402D-B658-B2831E0E8B86}" name="Brief Code Description (500 character max)" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{FB5B5AA8-A010-407A-8A2C-497F47B2889B}" name="Will the proposed project use or generate proprietary information, intellectual property, or restricted information?" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{B2E5C6A5-8781-4FA5-A92E-C4E3857F559E}" name="Does this project use or generate code(s) or data that are subject to export control restrictions?" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{6ECB594D-F693-461E-932E-4951A7D9ED95}" name="Additional Comments" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{0420DE82-AF93-48EB-905E-6D6E97C7D46A}" name="Allocation Program or Source (If existing allocation will be used)" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{F1802CDB-6A94-45A1-B4B7-F47A46CBC422}" name="Machine" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{D0E49B48-EDA7-4D05-92EC-C7F04F018CEE}" name="Estimated Compute Need" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{9997A077-AD03-480D-AF28-F4401B03DEA1}" name="Compute Need Units" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{CD58E2CE-CF0D-48A0-804A-1D51CC263494}" name="Project Number " dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{57020889-5267-4603-94CB-C38C2ADD54FC}" name="Expected data storage (TB)" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{756AB4E2-DC44-402D-B658-B2831E0E8B86}" name="Brief Code Description (500 character max)" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{FB5B5AA8-A010-407A-8A2C-497F47B2889B}" name="Will the proposed project use or generate proprietary information, intellectual property, or restricted information?" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{B2E5C6A5-8781-4FA5-A92E-C4E3857F559E}" name="Does this project use or generate code(s) or data that are subject to export control restrictions?" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{6ECB594D-F693-461E-932E-4951A7D9ED95}" name="Additional Comments" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7FBA2BCC-3CBE-4D5F-81AF-097ED6C39A7C}" name="LightHouseFocusTopics" displayName="LightHouseFocusTopics" ref="A1:A99" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7FBA2BCC-3CBE-4D5F-81AF-097ED6C39A7C}" name="LightHouseFocusTopics" displayName="LightHouseFocusTopics" ref="A1:A99" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A1:A99" xr:uid="{7FBA2BCC-3CBE-4D5F-81AF-097ED6C39A7C}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{FA8DE9AA-AB20-4D15-956E-EC035046AD33}" name="Topics" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{FA8DE9AA-AB20-4D15-956E-EC035046AD33}" name="Topics" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2118,7 +2119,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB5DB07-3DD9-4567-8EBA-5758081F630C}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.1640625" customWidth="1"/>
@@ -2330,14 +2331,14 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" t="s">
         <v>172</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>151</v>
       </c>
       <c r="E14" s="32" t="s">
@@ -2347,7 +2348,7 @@
         <v>148</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="1" t="s">
         <v>180</v>
       </c>
     </row>
@@ -2362,7 +2363,7 @@
       <c r="D15" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="32" t="s">
         <v>177</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -2373,8 +2374,11 @@
         <v>179</v>
       </c>
     </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H17" s="37"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E7:E15">
+  <conditionalFormatting sqref="E15 E7:E13">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>NOT(ISNUMBER(FIND(".",E7))*  ISNUMBER(FIND(".",E7, FIND("@",E7)))*  NOT(ISNUMBER(FIND(" ",E7)))*  NOT(ISNUMBER(FIND(",",E7))))</formula>
     </cfRule>
@@ -2385,19 +2389,20 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E14" r:id="rId1" xr:uid="{F7A0B885-0582-304A-9F5E-E382A0307A26}"/>
-    <hyperlink ref="E13" r:id="rId2" xr:uid="{2101755A-68CD-FD4C-96E9-552D5357388E}"/>
-    <hyperlink ref="E12" r:id="rId3" xr:uid="{ED358207-4683-9D4D-B716-9FA98B512656}"/>
-    <hyperlink ref="E11" r:id="rId4" xr:uid="{DFC89E7C-EAF8-B447-8927-8EE384ACC1DA}"/>
-    <hyperlink ref="E10" r:id="rId5" xr:uid="{33BE4541-BA9F-8745-A7B0-93EB0BABE011}"/>
-    <hyperlink ref="E9" r:id="rId6" xr:uid="{807E931C-BFE2-0648-9A14-E5411EEC7405}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{390F09B9-21AB-C345-914D-C5E695DE2EA7}"/>
-    <hyperlink ref="E7" r:id="rId8" xr:uid="{D67F019C-3D13-FA47-B2CB-5C05A2E4E71B}"/>
+    <hyperlink ref="E13" r:id="rId1" xr:uid="{2101755A-68CD-FD4C-96E9-552D5357388E}"/>
+    <hyperlink ref="E12" r:id="rId2" xr:uid="{ED358207-4683-9D4D-B716-9FA98B512656}"/>
+    <hyperlink ref="E11" r:id="rId3" xr:uid="{DFC89E7C-EAF8-B447-8927-8EE384ACC1DA}"/>
+    <hyperlink ref="E10" r:id="rId4" xr:uid="{33BE4541-BA9F-8745-A7B0-93EB0BABE011}"/>
+    <hyperlink ref="E9" r:id="rId5" xr:uid="{807E931C-BFE2-0648-9A14-E5411EEC7405}"/>
+    <hyperlink ref="E8" r:id="rId6" xr:uid="{390F09B9-21AB-C345-914D-C5E695DE2EA7}"/>
+    <hyperlink ref="E7" r:id="rId7" xr:uid="{D67F019C-3D13-FA47-B2CB-5C05A2E4E71B}"/>
+    <hyperlink ref="E14" r:id="rId8" xr:uid="{CD60FE2C-3110-AE4C-83E3-FEED95F71786}"/>
+    <hyperlink ref="E15" r:id="rId9" xr:uid="{85BCB193-3D60-DB49-BB39-D3982D85A268}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId9"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId10"/>
   <tableParts count="1">
-    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3377,15 +3382,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008CED8A1AE34AF041A1E9A24C685B4EF2" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="984bbabcfbc88371067310f4a94a943d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6e9a39fa-9558-409c-8ae5-a10906cd66e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="731bef58e6cb14d749b102d6e6e36026" ns2:_="">
     <xsd:import namespace="6e9a39fa-9558-409c-8ae5-a10906cd66e6"/>
@@ -3523,6 +3519,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{372A8FBF-BBB4-4216-BA26-BA4CC548C3A1}">
   <ds:schemaRefs>
@@ -3533,14 +3538,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9D4DF9D-E474-498E-A088-9C55A70986A7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2B5DBBD-F538-439A-A6E8-BCAD40A1ECB1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3556,4 +3553,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9D4DF9D-E474-498E-A088-9C55A70986A7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>